--- a/output/2026-09-20_21_Croazia_Istarska_ATEX_Equipment-Services.xlsx
+++ b/output/2026-09-20_21_Croazia_Istarska_ATEX_Equipment-Services.xlsx
@@ -526,7 +526,6 @@
           <t>+385 52 223 480 / 052 214 946 / 052 210 221</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Distributore/rappresentante ABB e materiale elettrico industriale (oltre 30.000 articoli a catalogo). Nessuna menzione esplicita di prodotti Ex/ATEX specifici nelle fonti trovate; pertinenza plausibile ma non certa tramite gamma ABB. Nessuna email generica verificata.</t>
@@ -571,7 +570,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Centro autorizzato Kärcher a Pula (Splitska 7). Confermato dal sito ufficiale Kärcher che offre aspiratori industriali certificati per Zona ATEX 22, classi polvere M e H - pertinenza diretta al settore ATEX.</t>
+          <t>Centro autorizzato Kärcher a Pula (Splitska 7). Confermato dal sito ufficiale Kärcher che offre aspiratori industriali certificati per Zona ATEX 22, classi polvere M e H - pertinenza diretta al settore ATEX. [DUPLICATO — vedi anche: 2026-09-20_17_Croazia_Istarska_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
